--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/73.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/73.xlsx
@@ -426,13 +426,13 @@
         <v>-4.924690674654633</v>
       </c>
       <c r="E2">
-        <v>-8.018349106863129</v>
+        <v>-6.932914643490612</v>
       </c>
       <c r="F2">
-        <v>-3.626031003604645</v>
+        <v>-3.883912544872368</v>
       </c>
       <c r="G2">
-        <v>-8.612676699089782</v>
+        <v>-8.858911765755234</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.927273120279064</v>
       </c>
       <c r="E3">
-        <v>-8.544231736425871</v>
+        <v>-6.759954107241651</v>
       </c>
       <c r="F3">
-        <v>-3.73017666695421</v>
+        <v>-3.78269267518949</v>
       </c>
       <c r="G3">
-        <v>-8.386261868567948</v>
+        <v>-8.882664929999505</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.063629954774575</v>
       </c>
       <c r="E4">
-        <v>-8.54044140368145</v>
+        <v>-8.316377038255929</v>
       </c>
       <c r="F4">
-        <v>-3.570509678432008</v>
+        <v>-3.507596830924192</v>
       </c>
       <c r="G4">
-        <v>-8.634479952011423</v>
+        <v>-9.130287115245912</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.303019671552523</v>
       </c>
       <c r="E5">
-        <v>-8.774558981404001</v>
+        <v>-8.160606589340084</v>
       </c>
       <c r="F5">
-        <v>-3.53841706851275</v>
+        <v>-3.557970681055832</v>
       </c>
       <c r="G5">
-        <v>-8.242253137609652</v>
+        <v>-9.054326647847335</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.601396853302945</v>
       </c>
       <c r="E6">
-        <v>-9.192346936403652</v>
+        <v>-10.06836664776546</v>
       </c>
       <c r="F6">
-        <v>-3.462867476275227</v>
+        <v>-3.663524568990157</v>
       </c>
       <c r="G6">
-        <v>-8.953176239440442</v>
+        <v>-9.13960630093896</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.911291064676339</v>
       </c>
       <c r="E7">
-        <v>-11.12221953340848</v>
+        <v>-10.03772246415556</v>
       </c>
       <c r="F7">
-        <v>-3.064230574291215</v>
+        <v>-3.274422175812367</v>
       </c>
       <c r="G7">
-        <v>-8.898025861301724</v>
+        <v>-9.837664622804143</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.188327014829706</v>
       </c>
       <c r="E8">
-        <v>-10.53406132929226</v>
+        <v>-9.607703100861185</v>
       </c>
       <c r="F8">
-        <v>-3.10457786537937</v>
+        <v>-3.132535265223854</v>
       </c>
       <c r="G8">
-        <v>-9.13270050294404</v>
+        <v>-9.482386807166177</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.386264921363801</v>
       </c>
       <c r="E9">
-        <v>-12.27737438260309</v>
+        <v>-10.85309232313263</v>
       </c>
       <c r="F9">
-        <v>-3.211072778683275</v>
+        <v>-3.0353760525495</v>
       </c>
       <c r="G9">
-        <v>-8.658723076995505</v>
+        <v>-10.1552849829329</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.467218520143157</v>
       </c>
       <c r="E10">
-        <v>-12.31437654371977</v>
+        <v>-11.16004134832055</v>
       </c>
       <c r="F10">
-        <v>-2.852693704107916</v>
+        <v>-2.82446625649012</v>
       </c>
       <c r="G10">
-        <v>-9.87583852341748</v>
+        <v>-10.33670287848496</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.40908545193706</v>
       </c>
       <c r="E11">
-        <v>-12.6535139621542</v>
+        <v>-12.26135717003796</v>
       </c>
       <c r="F11">
-        <v>-2.821145331572297</v>
+        <v>-2.760976036902552</v>
       </c>
       <c r="G11">
-        <v>-9.378823011061156</v>
+        <v>-10.33365055549775</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.206966758771313</v>
       </c>
       <c r="E12">
-        <v>-12.8955156131241</v>
+        <v>-12.35858350698264</v>
       </c>
       <c r="F12">
-        <v>-2.416786895937149</v>
+        <v>-2.517918130307927</v>
       </c>
       <c r="G12">
-        <v>-8.97548931637513</v>
+        <v>-10.05897459210442</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.872948170811925</v>
       </c>
       <c r="E13">
-        <v>-13.16043587104683</v>
+        <v>-13.31972041579262</v>
       </c>
       <c r="F13">
-        <v>-2.159094222437265</v>
+        <v>-2.450124542062815</v>
       </c>
       <c r="G13">
-        <v>-9.298022526084164</v>
+        <v>-9.685535123638015</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.44300660124439</v>
       </c>
       <c r="E14">
-        <v>-13.78565057796782</v>
+        <v>-14.45062981515017</v>
       </c>
       <c r="F14">
-        <v>-2.019206162391707</v>
+        <v>-1.91318673197701</v>
       </c>
       <c r="G14">
-        <v>-9.074527596727966</v>
+        <v>-9.832748462678325</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.970582577729743</v>
       </c>
       <c r="E15">
-        <v>-14.14289736395893</v>
+        <v>-14.62696859300885</v>
       </c>
       <c r="F15">
-        <v>-1.70589275963085</v>
+        <v>-1.778590282900535</v>
       </c>
       <c r="G15">
-        <v>-9.042415304997036</v>
+        <v>-9.480440206389085</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.512847726201245</v>
       </c>
       <c r="E16">
-        <v>-15.0667785171078</v>
+        <v>-15.07447692292084</v>
       </c>
       <c r="F16">
-        <v>-1.677941158358186</v>
+        <v>-1.566003042850486</v>
       </c>
       <c r="G16">
-        <v>-8.632669083601442</v>
+        <v>-8.608022072061567</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.121322880336738</v>
       </c>
       <c r="E17">
-        <v>-16.31126204457772</v>
+        <v>-16.39918236743664</v>
       </c>
       <c r="F17">
-        <v>-1.457510107371029</v>
+        <v>-1.479547165387705</v>
       </c>
       <c r="G17">
-        <v>-7.426077861448811</v>
+        <v>-7.854627981507466</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.83929253780074</v>
       </c>
       <c r="E18">
-        <v>-16.10048875036471</v>
+        <v>-17.16639190534214</v>
       </c>
       <c r="F18">
-        <v>-1.044848945257622</v>
+        <v>-1.028543361300917</v>
       </c>
       <c r="G18">
-        <v>-7.072246754211507</v>
+        <v>-8.002907316211424</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.69376670357252</v>
       </c>
       <c r="E19">
-        <v>-16.67702236170324</v>
+        <v>-17.90988582486947</v>
       </c>
       <c r="F19">
-        <v>-0.9328056270897667</v>
+        <v>-1.02759736572692</v>
       </c>
       <c r="G19">
-        <v>-6.137212961554214</v>
+        <v>-7.295258343918971</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.690817694497347</v>
       </c>
       <c r="E20">
-        <v>-18.08776428389077</v>
+        <v>-18.19746656672658</v>
       </c>
       <c r="F20">
-        <v>-1.06210798009495</v>
+        <v>-0.7154453340647876</v>
       </c>
       <c r="G20">
-        <v>-5.860914830846641</v>
+        <v>-7.03071264987581</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.823366883606199</v>
       </c>
       <c r="E21">
-        <v>-18.9181052779372</v>
+        <v>-19.3845064014092</v>
       </c>
       <c r="F21">
-        <v>-0.9988240239906788</v>
+        <v>-0.2603601637844064</v>
       </c>
       <c r="G21">
-        <v>-5.451486421822816</v>
+        <v>-5.845540657362265</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.070549713701777</v>
       </c>
       <c r="E22">
-        <v>-19.87160717957025</v>
+        <v>-19.7932917500816</v>
       </c>
       <c r="F22">
-        <v>-0.4735496269362899</v>
+        <v>-0.6282265302240276</v>
       </c>
       <c r="G22">
-        <v>-4.975039328901985</v>
+        <v>-6.457173877379234</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.397480913289471</v>
       </c>
       <c r="E23">
-        <v>-20.39499009148076</v>
+        <v>-20.33388286322126</v>
       </c>
       <c r="F23">
-        <v>-0.5654702441553399</v>
+        <v>-0.1899000608696832</v>
       </c>
       <c r="G23">
-        <v>-4.014782489780984</v>
+        <v>-5.191555628261399</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.76422648256706</v>
       </c>
       <c r="E24">
-        <v>-20.28769695681703</v>
+        <v>-21.73904570543133</v>
       </c>
       <c r="F24">
-        <v>-0.4035583799715513</v>
+        <v>0.02580681081930804</v>
       </c>
       <c r="G24">
-        <v>-3.734236929146526</v>
+        <v>-5.73772943133036</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.13316677448178</v>
       </c>
       <c r="E25">
-        <v>-21.88456821766782</v>
+        <v>-21.93732041138317</v>
       </c>
       <c r="F25">
-        <v>-0.2152315360472921</v>
+        <v>0.04263343787237441</v>
       </c>
       <c r="G25">
-        <v>-3.966170439082326</v>
+        <v>-5.620118990502212</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.46625896329896</v>
       </c>
       <c r="E26">
-        <v>-21.79522142549648</v>
+        <v>-22.76089586526215</v>
       </c>
       <c r="F26">
-        <v>-0.3760822615880945</v>
+        <v>0.2370844020055304</v>
       </c>
       <c r="G26">
-        <v>-3.481245039035422</v>
+        <v>-5.412988087746631</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.727076094827816</v>
       </c>
       <c r="E27">
-        <v>-22.54672621554338</v>
+        <v>-22.78116078644647</v>
       </c>
       <c r="F27">
-        <v>-0.5812572701178929</v>
+        <v>0.02397694722652394</v>
       </c>
       <c r="G27">
-        <v>-4.160390214234749</v>
+        <v>-5.513751162325428</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.8898968951923</v>
       </c>
       <c r="E28">
-        <v>-22.10875938036555</v>
+        <v>-23.23219226913643</v>
       </c>
       <c r="F28">
-        <v>-0.6431462555158495</v>
+        <v>-0.009026866835813965</v>
       </c>
       <c r="G28">
-        <v>-3.917154501827877</v>
+        <v>-5.940881058347736</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.937839270041069</v>
       </c>
       <c r="E29">
-        <v>-22.32782883896061</v>
+        <v>-22.94507796010211</v>
       </c>
       <c r="F29">
-        <v>-0.6889160396227306</v>
+        <v>0.06933834620382487</v>
       </c>
       <c r="G29">
-        <v>-4.154600070086564</v>
+        <v>-6.053777282327962</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.862256068019374</v>
       </c>
       <c r="E30">
-        <v>-21.94875480825253</v>
+        <v>-22.37433626701939</v>
       </c>
       <c r="F30">
-        <v>-0.724091004647806</v>
+        <v>-0.1695752382745946</v>
       </c>
       <c r="G30">
-        <v>-4.442120950172266</v>
+        <v>-5.642534694348616</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.663895460512212</v>
       </c>
       <c r="E31">
-        <v>-22.12184214177371</v>
+        <v>-23.33188662441529</v>
       </c>
       <c r="F31">
-        <v>-0.8090972391556884</v>
+        <v>-0.4941088775063708</v>
       </c>
       <c r="G31">
-        <v>-4.467112258448224</v>
+        <v>-5.809303425889403</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.352288407210685</v>
       </c>
       <c r="E32">
-        <v>-21.668596235294</v>
+        <v>-22.61943992268455</v>
       </c>
       <c r="F32">
-        <v>-0.9708177504694303</v>
+        <v>-0.5223876839031404</v>
       </c>
       <c r="G32">
-        <v>-4.466370696247427</v>
+        <v>-5.760899939559718</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.94163510505272</v>
       </c>
       <c r="E33">
-        <v>-22.26796241257921</v>
+        <v>-22.62144603666994</v>
       </c>
       <c r="F33">
-        <v>-1.092347532134146</v>
+        <v>-0.6350125159877612</v>
       </c>
       <c r="G33">
-        <v>-4.994227250847601</v>
+        <v>-5.878758671303312</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.449216950572938</v>
       </c>
       <c r="E34">
-        <v>-21.28693191745354</v>
+        <v>-22.16197800690369</v>
       </c>
       <c r="F34">
-        <v>-1.119218942313559</v>
+        <v>-0.335040798616393</v>
       </c>
       <c r="G34">
-        <v>-4.758215148807419</v>
+        <v>-5.517912518068292</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.899434626711353</v>
       </c>
       <c r="E35">
-        <v>-21.22373706267649</v>
+        <v>-21.19141734368375</v>
       </c>
       <c r="F35">
-        <v>-0.7893812666016574</v>
+        <v>-0.7090693901654398</v>
       </c>
       <c r="G35">
-        <v>-4.926483557477495</v>
+        <v>-5.709050175323653</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.318852620508493</v>
       </c>
       <c r="E36">
-        <v>-21.43494056192024</v>
+        <v>-21.27458276883462</v>
       </c>
       <c r="F36">
-        <v>-0.9934321805658568</v>
+        <v>-0.9111123415452532</v>
       </c>
       <c r="G36">
-        <v>-4.790380409266978</v>
+        <v>-5.367014541842772</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.734336801434188</v>
       </c>
       <c r="E37">
-        <v>-21.00225845590936</v>
+        <v>-21.54865507272685</v>
       </c>
       <c r="F37">
-        <v>-1.078119493623662</v>
+        <v>-1.169648293061187</v>
       </c>
       <c r="G37">
-        <v>-4.34208288506657</v>
+        <v>-4.778575003873936</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.173702680665738</v>
       </c>
       <c r="E38">
-        <v>-20.21126084404156</v>
+        <v>-20.34600558813979</v>
       </c>
       <c r="F38">
-        <v>-1.097901735569917</v>
+        <v>-0.9219142524777587</v>
       </c>
       <c r="G38">
-        <v>-4.449122753987825</v>
+        <v>-5.231474186373931</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.66470512382337</v>
       </c>
       <c r="E39">
-        <v>-20.57188587164239</v>
+        <v>-21.67424324238157</v>
       </c>
       <c r="F39">
-        <v>-1.291998986822077</v>
+        <v>-1.098064923948268</v>
       </c>
       <c r="G39">
-        <v>-4.142046481401647</v>
+        <v>-4.381928611177237</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.22821044454894</v>
       </c>
       <c r="E40">
-        <v>-20.9606644221489</v>
+        <v>-20.98520875127048</v>
       </c>
       <c r="F40">
-        <v>-1.483838936901609</v>
+        <v>-1.465667869553799</v>
       </c>
       <c r="G40">
-        <v>-4.357139246179175</v>
+        <v>-4.575002937573072</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.8750539527404745</v>
       </c>
       <c r="E41">
-        <v>-19.94852331059053</v>
+        <v>-20.53402782893826</v>
       </c>
       <c r="F41">
-        <v>-1.219894574612797</v>
+        <v>-1.101913518901674</v>
       </c>
       <c r="G41">
-        <v>-3.692666408809898</v>
+        <v>-4.215795504379991</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.6106026675620392</v>
       </c>
       <c r="E42">
-        <v>-19.95578245442483</v>
+        <v>-20.52800043003406</v>
       </c>
       <c r="F42">
-        <v>-1.351967816580344</v>
+        <v>-1.342819326983827</v>
       </c>
       <c r="G42">
-        <v>-3.609988844512139</v>
+        <v>-4.977979093340857</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.4318483411023916</v>
       </c>
       <c r="E43">
-        <v>-19.52843489079498</v>
+        <v>-19.77524578116103</v>
       </c>
       <c r="F43">
-        <v>-1.452377542943284</v>
+        <v>-1.385480248228001</v>
       </c>
       <c r="G43">
-        <v>-4.168765894449105</v>
+        <v>-4.440720589409154</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.3278835246597921</v>
       </c>
       <c r="E44">
-        <v>-18.85639576263468</v>
+        <v>-19.61240638431921</v>
       </c>
       <c r="F44">
-        <v>-1.673265852736786</v>
+        <v>-1.579307451706849</v>
       </c>
       <c r="G44">
-        <v>-3.760996068740455</v>
+        <v>-4.20076893817724</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.2857347150687038</v>
       </c>
       <c r="E45">
-        <v>-17.99555549614658</v>
+        <v>-18.92160578834513</v>
       </c>
       <c r="F45">
-        <v>-1.347189793400997</v>
+        <v>-1.205224187909218</v>
       </c>
       <c r="G45">
-        <v>-3.466062877192324</v>
+        <v>-3.935110900832884</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.2899543726248158</v>
       </c>
       <c r="E46">
-        <v>-17.93861446397414</v>
+        <v>-19.20124358679278</v>
       </c>
       <c r="F46">
-        <v>-1.844019710578056</v>
+        <v>-1.706618409475702</v>
       </c>
       <c r="G46">
-        <v>-3.986718995244583</v>
+        <v>-3.189599219207787</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.3215463819488194</v>
       </c>
       <c r="E47">
-        <v>-18.38955537718394</v>
+        <v>-18.64933128863395</v>
       </c>
       <c r="F47">
-        <v>-1.624142837383372</v>
+        <v>-1.66518015851806</v>
       </c>
       <c r="G47">
-        <v>-3.157662386390438</v>
+        <v>-3.578191054607439</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.3591201641911641</v>
       </c>
       <c r="E48">
-        <v>-18.14408491512416</v>
+        <v>-18.5780983924933</v>
       </c>
       <c r="F48">
-        <v>-1.708372891634832</v>
+        <v>-1.461643660710999</v>
       </c>
       <c r="G48">
-        <v>-3.277335297089552</v>
+        <v>-3.832719037848765</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.3834226766185416</v>
       </c>
       <c r="E49">
-        <v>-18.11626649929504</v>
+        <v>-17.66205149937769</v>
       </c>
       <c r="F49">
-        <v>-1.798891911208345</v>
+        <v>-1.941056324876796</v>
       </c>
       <c r="G49">
-        <v>-3.268300818312881</v>
+        <v>-3.815676349412597</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.3786530189781215</v>
       </c>
       <c r="E50">
-        <v>-17.81555318281569</v>
+        <v>-17.42268994875426</v>
       </c>
       <c r="F50">
-        <v>-1.701660630569947</v>
+        <v>-1.70244840797001</v>
       </c>
       <c r="G50">
-        <v>-3.246636608303891</v>
+        <v>-2.976800662488975</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.3348810148030419</v>
       </c>
       <c r="E51">
-        <v>-17.10284835806651</v>
+        <v>-17.5481694350328</v>
       </c>
       <c r="F51">
-        <v>-1.769444278406225</v>
+        <v>-1.90580432168326</v>
       </c>
       <c r="G51">
-        <v>-3.076868522504525</v>
+        <v>-3.766153898690639</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.2502817081310596</v>
       </c>
       <c r="E52">
-        <v>-17.38086043434541</v>
+        <v>-16.89085690434544</v>
       </c>
       <c r="F52">
-        <v>-2.16054552212697</v>
+        <v>-1.929397053682393</v>
       </c>
       <c r="G52">
-        <v>-3.50419043016811</v>
+        <v>-3.737792455055703</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.1310980974146847</v>
       </c>
       <c r="E53">
-        <v>-15.83378427368296</v>
+        <v>-16.52990129814205</v>
       </c>
       <c r="F53">
-        <v>-2.116133432193277</v>
+        <v>-1.955582575652288</v>
       </c>
       <c r="G53">
-        <v>-3.041379474323538</v>
+        <v>-3.094930858966789</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.009008360510578165</v>
       </c>
       <c r="E54">
-        <v>-15.57860023487673</v>
+        <v>-17.1277594935827</v>
       </c>
       <c r="F54">
-        <v>-2.320018672676917</v>
+        <v>-2.093271320243414</v>
       </c>
       <c r="G54">
-        <v>-3.373185522088071</v>
+        <v>-3.935144006288277</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.1514572850244285</v>
       </c>
       <c r="E55">
-        <v>-15.58311965193638</v>
+        <v>-16.55896504432328</v>
       </c>
       <c r="F55">
-        <v>-2.28858627157769</v>
+        <v>-2.202350739844053</v>
       </c>
       <c r="G55">
-        <v>-3.129188384207167</v>
+        <v>-4.190052702266619</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.2744939558700274</v>
       </c>
       <c r="E56">
-        <v>-15.41052139360804</v>
+        <v>-16.48971561979798</v>
       </c>
       <c r="F56">
-        <v>-2.158409990962553</v>
+        <v>-2.162387811230796</v>
       </c>
       <c r="G56">
-        <v>-3.19858403980137</v>
+        <v>-3.563853081876856</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.3569720540297938</v>
       </c>
       <c r="E57">
-        <v>-15.89239631276424</v>
+        <v>-15.15973450306325</v>
       </c>
       <c r="F57">
-        <v>-2.50348217157934</v>
+        <v>-2.625967060859483</v>
       </c>
       <c r="G57">
-        <v>-3.254555433233827</v>
+        <v>-3.600927881371154</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.3810745227374129</v>
       </c>
       <c r="E58">
-        <v>-15.72669039187556</v>
+        <v>-14.75414172856626</v>
       </c>
       <c r="F58">
-        <v>-2.604047631014005</v>
+        <v>-2.17664815606999</v>
       </c>
       <c r="G58">
-        <v>-3.382451739052491</v>
+        <v>-4.136127225977431</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.3349839735842535</v>
       </c>
       <c r="E59">
-        <v>-14.83102163179447</v>
+        <v>-14.97595997088397</v>
       </c>
       <c r="F59">
-        <v>-2.36981929256582</v>
+        <v>-2.634215943456561</v>
       </c>
       <c r="G59">
-        <v>-3.737395189590991</v>
+        <v>-4.839297030155248</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.2136279367552981</v>
       </c>
       <c r="E60">
-        <v>-14.99143376656818</v>
+        <v>-15.03146094832198</v>
       </c>
       <c r="F60">
-        <v>-2.709711691812902</v>
+        <v>-2.431907914507851</v>
       </c>
       <c r="G60">
-        <v>-3.1119603052208</v>
+        <v>-4.508275581683522</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.02082940284526761</v>
       </c>
       <c r="E61">
-        <v>-14.80540858280709</v>
+        <v>-14.28297665043819</v>
       </c>
       <c r="F61">
-        <v>-2.5703728393554</v>
+        <v>-2.638496946194229</v>
       </c>
       <c r="G61">
-        <v>-3.321881997865986</v>
+        <v>-4.129575656355213</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.2315451923886593</v>
       </c>
       <c r="E62">
-        <v>-14.53391298062523</v>
+        <v>-14.92320777716862</v>
       </c>
       <c r="F62">
-        <v>-2.720415027024475</v>
+        <v>-2.342198209886873</v>
       </c>
       <c r="G62">
-        <v>-4.276315587383408</v>
+        <v>-5.140225619674999</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.5261114904823749</v>
       </c>
       <c r="E63">
-        <v>-14.14602653949823</v>
+        <v>-14.43212647035482</v>
       </c>
       <c r="F63">
-        <v>-2.528980148604912</v>
+        <v>-2.650007939623531</v>
       </c>
       <c r="G63">
-        <v>-4.81194199236425</v>
+        <v>-4.732164465958894</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.841705351932343</v>
       </c>
       <c r="E64">
-        <v>-14.74038875300496</v>
+        <v>-13.82292444752495</v>
       </c>
       <c r="F64">
-        <v>-2.611134314144955</v>
+        <v>-2.535307218827494</v>
       </c>
       <c r="G64">
-        <v>-4.336100729277106</v>
+        <v>-5.07871899410088</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.155263505367264</v>
       </c>
       <c r="E65">
-        <v>-14.29039881933677</v>
+        <v>-13.2294362295017</v>
       </c>
       <c r="F65">
-        <v>-2.732579602334585</v>
+        <v>-2.734958673515425</v>
       </c>
       <c r="G65">
-        <v>-4.746893083063111</v>
+        <v>-5.043805980843726</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.444299347881114</v>
       </c>
       <c r="E66">
-        <v>-14.37644888243052</v>
+        <v>-14.41078830083068</v>
       </c>
       <c r="F66">
-        <v>-2.662817813140422</v>
+        <v>-2.617705752751364</v>
       </c>
       <c r="G66">
-        <v>-4.569355146883075</v>
+        <v>-5.638191258601092</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.691979141504929</v>
       </c>
       <c r="E67">
-        <v>-14.40366048274261</v>
+        <v>-13.91655970458155</v>
       </c>
       <c r="F67">
-        <v>-2.66476116306739</v>
+        <v>-2.739911482216764</v>
       </c>
       <c r="G67">
-        <v>-5.032927528201681</v>
+        <v>-5.321560751588579</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.886998435181467</v>
       </c>
       <c r="E68">
-        <v>-13.59949406846051</v>
+        <v>-13.88278181695834</v>
       </c>
       <c r="F68">
-        <v>-2.685341951189943</v>
+        <v>-2.663815167493393</v>
       </c>
       <c r="G68">
-        <v>-4.908854902480875</v>
+        <v>-5.774767814823726</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.024890650911889</v>
       </c>
       <c r="E69">
-        <v>-13.94797825724677</v>
+        <v>-14.35143359201215</v>
       </c>
       <c r="F69">
-        <v>-2.912535793653555</v>
+        <v>-2.852681278596874</v>
       </c>
       <c r="G69">
-        <v>-4.759565851387441</v>
+        <v>-6.529717861781284</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.108162897639005</v>
       </c>
       <c r="E70">
-        <v>-13.87759218574555</v>
+        <v>-13.39293225507463</v>
       </c>
       <c r="F70">
-        <v>-2.73033804014261</v>
+        <v>-2.914962081776355</v>
       </c>
       <c r="G70">
-        <v>-5.038929547264379</v>
+        <v>-6.449410648089644</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.145092171640581</v>
       </c>
       <c r="E71">
-        <v>-14.31451294342761</v>
+        <v>-14.00587932590884</v>
       </c>
       <c r="F71">
-        <v>-2.772418275837422</v>
+        <v>-2.735623024172471</v>
       </c>
       <c r="G71">
-        <v>-4.900403079719116</v>
+        <v>-5.070932590992514</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.145997007741239</v>
       </c>
       <c r="E72">
-        <v>-14.25542994304953</v>
+        <v>-13.58924613178115</v>
       </c>
       <c r="F72">
-        <v>-2.703326635872124</v>
+        <v>-2.916596450662079</v>
       </c>
       <c r="G72">
-        <v>-5.127033095701004</v>
+        <v>-6.178727202616674</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.121123321195238</v>
       </c>
       <c r="E73">
-        <v>-13.87863826324132</v>
+        <v>-14.11559519416668</v>
       </c>
       <c r="F73">
-        <v>-2.939122245446406</v>
+        <v>-2.997461676523367</v>
       </c>
       <c r="G73">
-        <v>-4.242763208342894</v>
+        <v>-5.791919751262689</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.083025050926858</v>
       </c>
       <c r="E74">
-        <v>-15.37115989753337</v>
+        <v>-14.92200773155659</v>
       </c>
       <c r="F74">
-        <v>-2.957854945893314</v>
+        <v>-2.900758065920552</v>
       </c>
       <c r="G74">
-        <v>-4.730489329916022</v>
+        <v>-6.129194820258099</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.044200220539716</v>
       </c>
       <c r="E75">
-        <v>-15.12519130333274</v>
+        <v>-14.75843925039953</v>
       </c>
       <c r="F75">
-        <v>-3.112248547529294</v>
+        <v>-3.013189060032918</v>
       </c>
       <c r="G75">
-        <v>-4.588496721191142</v>
+        <v>-6.506368584092804</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.014565953171959</v>
       </c>
       <c r="E76">
-        <v>-15.35925906784121</v>
+        <v>-15.29205651356738</v>
       </c>
       <c r="F76">
-        <v>-3.233649103879173</v>
+        <v>-3.344570812583638</v>
       </c>
       <c r="G76">
-        <v>-4.275464777179815</v>
+        <v>-5.508235793457002</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.001732487444517</v>
       </c>
       <c r="E77">
-        <v>-15.01761287480652</v>
+        <v>-15.29607779848619</v>
       </c>
       <c r="F77">
-        <v>-3.200638662877612</v>
+        <v>-3.056322150696688</v>
       </c>
       <c r="G77">
-        <v>-4.157370996702934</v>
+        <v>-6.01149499470039</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.009823356101032</v>
       </c>
       <c r="E78">
-        <v>-15.87210874920988</v>
+        <v>-15.48966100536608</v>
       </c>
       <c r="F78">
-        <v>-3.138429099294772</v>
+        <v>-3.260257921591899</v>
       </c>
       <c r="G78">
-        <v>-4.526976853434865</v>
+        <v>-5.542125848142521</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.037895872003503</v>
       </c>
       <c r="E79">
-        <v>-17.40593459492588</v>
+        <v>-16.28024652609918</v>
       </c>
       <c r="F79">
-        <v>-3.333871619209079</v>
+        <v>-3.382817363938293</v>
       </c>
       <c r="G79">
-        <v>-3.986626299969483</v>
+        <v>-6.160863498886767</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.083675289245907</v>
       </c>
       <c r="E80">
-        <v>-16.84632841942802</v>
+        <v>-16.89267282242251</v>
       </c>
       <c r="F80">
-        <v>-3.3585851323042</v>
+        <v>-3.239837836745488</v>
       </c>
       <c r="G80">
-        <v>-3.785960892652099</v>
+        <v>-4.589764660132682</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.146299838243403</v>
       </c>
       <c r="E81">
-        <v>-17.15248949013859</v>
+        <v>-17.31882939738834</v>
       </c>
       <c r="F81">
-        <v>-3.372263134859225</v>
+        <v>-3.200557482872138</v>
       </c>
       <c r="G81">
-        <v>-3.872525037412962</v>
+        <v>-4.595445556278072</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.222422188875106</v>
       </c>
       <c r="E82">
-        <v>-19.21255571486395</v>
+        <v>-18.44733870552182</v>
       </c>
       <c r="F82">
-        <v>-3.268849748293735</v>
+        <v>-3.465474348491837</v>
       </c>
       <c r="G82">
-        <v>-3.913608907555318</v>
+        <v>-4.907040723525355</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.307096249705238</v>
       </c>
       <c r="E83">
-        <v>-19.34116890515579</v>
+        <v>-19.64875191670478</v>
       </c>
       <c r="F83">
-        <v>-3.4619720111128</v>
+        <v>-3.245611557543</v>
       </c>
       <c r="G83">
-        <v>-4.056720480672472</v>
+        <v>-4.519120928870175</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.396687671288774</v>
       </c>
       <c r="E84">
-        <v>-20.54694303680814</v>
+        <v>-20.41462102630401</v>
       </c>
       <c r="F84">
-        <v>-3.407061192716027</v>
+        <v>-3.524473988388829</v>
       </c>
       <c r="G84">
-        <v>-3.635533013893156</v>
+        <v>-4.837741073751791</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.488248855053438</v>
       </c>
       <c r="E85">
-        <v>-20.84881111415945</v>
+        <v>-20.73573964666192</v>
       </c>
       <c r="F85">
-        <v>-3.57156667523798</v>
+        <v>-3.900534565176943</v>
       </c>
       <c r="G85">
-        <v>-3.898115554431528</v>
+        <v>-5.011067996005873</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.578339540231934</v>
       </c>
       <c r="E86">
-        <v>-21.94777212939287</v>
+        <v>-22.19777559393433</v>
       </c>
       <c r="F86">
-        <v>-3.552480261910077</v>
+        <v>-3.527371617563821</v>
       </c>
       <c r="G86">
-        <v>-3.76923932713324</v>
+        <v>-4.269681254122709</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.664523914643062</v>
       </c>
       <c r="E87">
-        <v>-23.59179386161152</v>
+        <v>-23.61646498800532</v>
       </c>
       <c r="F87">
-        <v>-3.522797372765563</v>
+        <v>-3.688194178612929</v>
       </c>
       <c r="G87">
-        <v>-3.374155511931078</v>
+        <v>-4.210041776232738</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.747009813032329</v>
       </c>
       <c r="E88">
-        <v>-25.42435408066553</v>
+        <v>-23.30372404456159</v>
       </c>
       <c r="F88">
-        <v>-3.532520749339623</v>
+        <v>-3.757463089202426</v>
       </c>
       <c r="G88">
-        <v>-3.648987070964754</v>
+        <v>-5.103740097286692</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.82499728646133</v>
       </c>
       <c r="E89">
-        <v>-26.35085269179084</v>
+        <v>-26.38886470261122</v>
       </c>
       <c r="F89">
-        <v>-3.799458831422152</v>
+        <v>-3.628111862520478</v>
       </c>
       <c r="G89">
-        <v>-3.14956810254692</v>
+        <v>-4.747459186350326</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.89854071391412</v>
       </c>
       <c r="E90">
-        <v>-28.26348991672247</v>
+        <v>-27.92066179197179</v>
       </c>
       <c r="F90">
-        <v>-3.71118882934724</v>
+        <v>-3.794440581695993</v>
       </c>
       <c r="G90">
-        <v>-3.072952147131567</v>
+        <v>-4.972675599386945</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.971642441150923</v>
       </c>
       <c r="E91">
-        <v>-29.33113200571885</v>
+        <v>-29.51138338512016</v>
       </c>
       <c r="F91">
-        <v>-3.506621014123694</v>
+        <v>-3.757924489845785</v>
       </c>
       <c r="G91">
-        <v>-4.010144415480466</v>
+        <v>-4.603460387028647</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.050422876969961</v>
       </c>
       <c r="E92">
-        <v>-31.16566211096619</v>
+        <v>-31.33352358548252</v>
       </c>
       <c r="F92">
-        <v>-3.413907649300165</v>
+        <v>-3.612721624543866</v>
       </c>
       <c r="G92">
-        <v>-3.15615608817007</v>
+        <v>-4.960959578723465</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.140884498729974</v>
       </c>
       <c r="E93">
-        <v>-33.61592203432546</v>
+        <v>-33.30811486331309</v>
       </c>
       <c r="F93">
-        <v>-3.525754644393557</v>
+        <v>-3.202106529915373</v>
       </c>
       <c r="G93">
-        <v>-4.6696315712676</v>
+        <v>-6.173191970475012</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.249073600283269</v>
       </c>
       <c r="E94">
-        <v>-35.2693833706131</v>
+        <v>-35.13913540120448</v>
       </c>
       <c r="F94">
-        <v>-3.328788756825502</v>
+        <v>-3.607762188903305</v>
       </c>
       <c r="G94">
-        <v>-4.250437052902925</v>
+        <v>-5.765594293134405</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.382492975420753</v>
       </c>
       <c r="E95">
-        <v>-37.19151680553882</v>
+        <v>-37.43509210122639</v>
       </c>
       <c r="F95">
-        <v>-3.135119771520588</v>
+        <v>-3.453588932996469</v>
       </c>
       <c r="G95">
-        <v>-4.343863958566697</v>
+        <v>-6.08031130482522</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.543306212839996</v>
       </c>
       <c r="E96">
-        <v>-39.60290204377924</v>
+        <v>-39.48436244391745</v>
       </c>
       <c r="F96">
-        <v>-3.492717695635107</v>
+        <v>-3.226720638922158</v>
       </c>
       <c r="G96">
-        <v>-4.968951235655265</v>
+        <v>-6.688994828766699</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.727938659349013</v>
       </c>
       <c r="E97">
-        <v>-41.45628645055751</v>
+        <v>-41.38498789154375</v>
       </c>
       <c r="F97">
-        <v>-2.991248092634967</v>
+        <v>-3.039206423420045</v>
       </c>
       <c r="G97">
-        <v>-5.368729404432115</v>
+        <v>-6.254459242373042</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.932357709910734</v>
       </c>
       <c r="E98">
-        <v>-43.78763317494936</v>
+        <v>-43.86238695963098</v>
       </c>
       <c r="F98">
-        <v>-3.083321957823535</v>
+        <v>-2.933496802413994</v>
       </c>
       <c r="G98">
-        <v>-4.957102793170214</v>
+        <v>-6.710033345668768</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.144324166486444</v>
       </c>
       <c r="E99">
-        <v>-46.60976459110751</v>
+        <v>-46.32504810906025</v>
       </c>
       <c r="F99">
-        <v>-3.003618103060973</v>
+        <v>-3.123926042806559</v>
       </c>
       <c r="G99">
-        <v>-5.876620058884943</v>
+        <v>-7.113320692717244</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.347236528584643</v>
       </c>
       <c r="E100">
-        <v>-48.25964390445508</v>
+        <v>-48.49862279902487</v>
       </c>
       <c r="F100">
-        <v>-3.002684532998017</v>
+        <v>-2.856953997660514</v>
       </c>
       <c r="G100">
-        <v>-6.010657426678955</v>
+        <v>-7.592071925333408</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.515385903257195</v>
       </c>
       <c r="E101">
-        <v>-50.88845702946278</v>
+        <v>-51.01048242219197</v>
       </c>
       <c r="F101">
-        <v>-2.807128526749527</v>
+        <v>-2.651608345445739</v>
       </c>
       <c r="G101">
-        <v>-6.626882373358893</v>
+        <v>-8.234956695241097</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.632747145447214</v>
       </c>
       <c r="E102">
-        <v>-53.47617651708788</v>
+        <v>-51.99838487662429</v>
       </c>
       <c r="F102">
-        <v>-2.738620057435799</v>
+        <v>-2.830724572218271</v>
       </c>
       <c r="G102">
-        <v>-7.669608212408678</v>
+        <v>-8.697469701987135</v>
       </c>
     </row>
   </sheetData>
